--- a/results/Int Task Remove ACC 0.5/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.5/Linea_fi_all.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.0091231178033658 +/- 0.0027242792735570815</t>
+          <t>-0.009078830823737815 +/- 0.002673774818090992</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.01942015646571559 +/- 0.007658589622720569</t>
+          <t>-0.019466175793833397 +/- 0.007578672201448274</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.027366447985004705 +/- 0.003281563523900961</t>
+          <t>0.027413308341143416 +/- 0.003200600059330679</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.014665970772442583 +/- 0.002304148231173689</t>
+          <t>-0.014718162839248428 +/- 0.0022485030509955995</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.032045929018789186 +/- 0.002622099517135819</t>
+          <t>0.03199373695198334 +/- 0.002546737557151558</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.025294950448324683 +/- 0.00632162418108176</t>
+          <t>0.02524775837659273 +/- 0.006279383519600244</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.04540311173974544 +/- 0.0040450858234420866</t>
+          <t>0.04530881659594534 +/- 0.004003103733545942</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.014313160422670567 +/- 0.004017391674606414</t>
+          <t>0.014361191162343957 +/- 0.004009631923811768</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.0028818443804035088 +/- 0.0010075012950721742</t>
+          <t>0.0028338136407301097 +/- 0.0010621202875838523</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.033490813648294 +/- 0.006376602473096136</t>
+          <t>0.03338582677165358 +/- 0.006434248166317911</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.02262467191601054 +/- 0.0037225954123866483</t>
+          <t>0.02257217847769034 +/- 0.003689508323528739</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.0011023622047243498 +/- 0.001295429152677489</t>
+          <t>-0.0011548556430445612 +/- 0.0012153109609228598</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0008979206049149147 +/- 0.0022211720226843128</t>
+          <t>0.0009451795841209587 +/- 0.0022266954611322794</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.03520793950850657 +/- 0.005091044686163372</t>
+          <t>0.03525519848771262 +/- 0.005117080409693449</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.035302457466918756 +/- 0.004735576101354245</t>
+          <t>-0.03525519848771271 +/- 0.004811140488704885</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
